--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%9e%d7%a8-%d7%90%d7%93%d7%9d-%d7%97%d7%9c%d7%a7-%d7%9e%d7%94%d7%a0%d7%a6%d7%97/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
+        <v>"משפחה וכבוד" הפותח את אלבומו העשירי  של עומר אדם מציב הצהרה אמנותית: זו אינה רק בלדת אהבה, אלא בלדה על מחיר ההצלחה. השיר יושב על קו התפר שבין עולם חומרי נוצץ לבין נאמנות פנימית, בין אהבה הרסנית לבין ערכי יסוד.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
     </row>
   </sheetData>
